--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0113.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0113.xlsx
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Ta nghe nói hai đứa ngươi có xích mích gì đó.</t>
+          <t>Tao nghe nói hai đứa mày có xích mích gì đó.</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Ta nghe nói hai đứa ngươi là bạn thân.</t>
+          <t>Tao nghe nói hai đứa mày là bạn thân.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Nhưng ta đã nghe thấy bánh răng bắt đầu chuyển động rồi!</t>
+          <t>Nhưng tao đã nghe thấy bánh răng bắt đầu chuyển động rồi!</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ta bảo mà! Chỉ cần một chút thời gian, một cơ hội và một chút dũng khí thôi.</t>
+          <t>Tao bảo mà! Chỉ cần một chút thời gian, một cơ hội và một chút dũng khí thôi.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Ai, ta á? Ta có làm gì đâu!</t>
+          <t>Ai, tao á? Tao có làm gì đâu!</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Đến lúc nói thật với ta đi.</t>
+          <t>Đến lúc nói thật với tao đi.</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Cầu Không Gian–Bjartr gần Khu Rừng Bjartr. Nếu bọn Lưu Đày dám gây rối ở đó... chắc chắn có gì đó không ổn.</t>
+          <t>Cầu Không Gian–Bjartr gần Khu Bjartr Woods. Nếu bọn Lưu Đày dám gây rối ở đó... chắc chắn có gì đó không ổn.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Ta phải đến Cầu Spacetrek–Bjartr ngay. Không thể để bọn Outcast gây rối trong Rừng Bjartr được.</t>
+          <t>Ta phải đến Cầu Spacetrek–Bjartr ngay. Không thể để bọn Outcast gây rối trong Bjartr Woods được.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Đừng bảo là chúng nó thực sự nhắm vào một tay lái tầm thường như ta chứ... Không đời nào, phải không?!</t>
+          <t>Đừng bảo là chúng nó thực sự nhắm vào một tay lái tầm thường như tao chứ... Không đời nào, phải không?!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ngươi đến nhanh thế. Kế hoạch của chúng ta là để Spacetrek Collective giải quyết chuyện này mà.</t>
+          <t>Mày đến nhanh thế. Kế hoạch của chúng ta là để Spacetrek Collective giải quyết chuyện này mà.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Cậu tìm cái gì vậy?</t>
+          <t>Mày tìm cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Nếu cậu muốn đăng ký thì dễ thôi. Ghé Spacetrek Archive sau giờ học buổi trưa là được. Ta sẽ có mặt ở đó từ 12 giờ đến 2 giờ chiều!</t>
+          <t>Nếu cậu muốn đăng ký thì dễ thôi. Ghé Spacetrek Archive sau giờ học buổi trưa là được. Tao sẽ có mặt ở đó từ 12 giờ đến 2 giờ chiều!</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Hả? Khoan, cậu là... {Male=anh;Female=chị} phải không?</t>
+          <t>Hả? Khoan, cậu là... {Male=him;Female=her} phải không?</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chính là ta.</t>
+          <t>Chính là tao.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Đây là…?</t>
+          <t>Cái này… là gì?</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Ừ, ừ. Chắc lần này ta sẽ là người kể chuyện cho cậu nghe.</t>
+          <t>Ừ, ừ. Chắc lần này tao sẽ là người kể chuyện cho cậu nghe.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Vì mấy đồng thù lao, ta nhận việc.</t>
+          <t>Vì mấy đồng thù lao, tao nhận việc.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Vì nụ cười của mọi người, ta đồng ý.</t>
+          <t>Vì nụ cười của mọi người, tao đồng ý.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Giữ chỗ cho ta nhé.</t>
+          <t>Giữ chỗ cho tao nhé.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Giữ chỗ cho ta nhé.</t>
+          <t>Giữ chỗ cho tao nhé.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Chuyện này xảy ra đột ngột quá. Ta cần chút thời gian để suy nghĩ đã.</t>
+          <t>Chuyện này xảy ra đột ngột quá. Tao cần chút thời gian để suy nghĩ đã.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Được rồi, đưa Thiết bị đầu cuối đây cho ta. Ta sẽ giúp sắp xếp mấy tấm hình và tải tất cả lên nộp luôn.</t>
+          <t>Được rồi, đưa Thiết bị đầu cuối đây cho tao. Tao sẽ giúp sắp xếp mấy tấm hình và tải tất cả lên nộp luôn.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Chỉ có trẻ con mới phải chọn lựa. Ta muốn tất cả cơ.</t>
+          <t>Chỉ có trẻ con mới phải chọn lựa. Tao muốn tất cả cơ.</t>
         </is>
       </c>
     </row>
